--- a/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna</t>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,44; 65,78</t>
+          <t>44,25; 66,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,65; 56,27</t>
+          <t>34,1; 56,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,02; 58,4</t>
+          <t>42,04; 57,2</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,1; 54,42</t>
+          <t>41,0; 54,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,04; 53,93</t>
+          <t>41,21; 54,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,93; 52,61</t>
+          <t>42,8; 52,16</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,12; 57,08</t>
+          <t>44,42; 58,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,94; 59,76</t>
+          <t>46,62; 59,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,31; 56,92</t>
+          <t>47,18; 57,26</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,17; 54,79</t>
+          <t>43,67; 55,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,39; 59,87</t>
+          <t>46,07; 60,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,69; 56,02</t>
+          <t>45,96; 55,05</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,94; 53,39</t>
+          <t>46,03; 53,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,13; 54,86</t>
+          <t>47,06; 54,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,7; 52,83</t>
+          <t>47,79; 52,99</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>25714</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20543</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46257</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20800; 31289</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15590; 25866</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38983; 53045</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>76213</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86133</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>162347</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>65140; 87181</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74615; 97911</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>145475; 177315</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>87016</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>113215</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>200231</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>76191; 99648</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99052; 127398</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>181183; 219900</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>118129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156190</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>274319</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>105298; 133468</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>138118; 179939</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>248636; 297808</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>307072</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>376082</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683154</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>284750; 328568</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>347770; 404953</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>648831; 719338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,25; 66,56</t>
+          <t>44,4; 65,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,1; 56,57</t>
+          <t>32,96; 56,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,04; 57,2</t>
+          <t>42,26; 57,88</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,0; 54,87</t>
+          <t>41,16; 54,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,21; 54,08</t>
+          <t>41,21; 54,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,8; 52,16</t>
+          <t>43,03; 52,29</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,42; 58,09</t>
+          <t>43,45; 56,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,62; 59,96</t>
+          <t>46,47; 59,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,18; 57,26</t>
+          <t>47,23; 56,76</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,67; 55,35</t>
+          <t>42,93; 55,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,02</t>
+          <t>45,19; 59,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,96; 55,05</t>
+          <t>46,32; 55,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,03; 53,12</t>
+          <t>46,3; 53,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,06; 54,79</t>
+          <t>47,2; 54,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,79; 52,99</t>
+          <t>47,61; 52,98</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20800; 31289</t>
+          <t>20871; 30920</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15590; 25866</t>
+          <t>15071; 25643</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38983; 53045</t>
+          <t>39184; 53678</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65140; 87181</t>
+          <t>65398; 86356</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74615; 97911</t>
+          <t>74615; 97960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145475; 177315</t>
+          <t>146286; 177742</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76191; 99648</t>
+          <t>74530; 97760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99052; 127398</t>
+          <t>98749; 126105</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181183; 219900</t>
+          <t>181368; 217953</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105298; 133468</t>
+          <t>103519; 133311</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138118; 179939</t>
+          <t>135463; 177085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>248636; 297808</t>
+          <t>250544; 302820</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>284750; 328568</t>
+          <t>286377; 329456</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>347770; 404953</t>
+          <t>348861; 404445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>648831; 719338</t>
+          <t>646341; 719224</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,4; 65,77</t>
+          <t>34,89; 57,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,96; 56,08</t>
+          <t>43,86; 65,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 57,88</t>
+          <t>42,2; 59,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,16; 54,35</t>
+          <t>40,74; 53,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,21; 54,11</t>
+          <t>42,81; 55,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,03; 52,29</t>
+          <t>43,42; 53,06</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,45; 56,99</t>
+          <t>44,44; 57,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,47; 59,35</t>
+          <t>43,59; 56,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,23; 56,76</t>
+          <t>46,09; 55,71</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,93; 55,28</t>
+          <t>46,41; 59,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,19; 59,07</t>
+          <t>41,54; 52,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,32; 55,98</t>
+          <t>45,35; 54,68</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,3; 53,26</t>
+          <t>46,79; 54,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,73</t>
+          <t>45,94; 52,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,61; 52,98</t>
+          <t>47,36; 52,2</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>23436</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>40701</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20871; 30920</t>
+          <t>13191; 21880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15071; 25643</t>
+          <t>18866; 28137</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39184; 53678</t>
+          <t>34108; 47832</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76213</t>
+          <t>73510</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86133</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162347</t>
+          <t>145314</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65398; 86356</t>
+          <t>63678; 83171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74615; 97960</t>
+          <t>62139; 80842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146286; 177742</t>
+          <t>130891; 159943</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>121</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>101973</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113215</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200231</t>
+          <t>190017</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>74530; 97760</t>
+          <t>88935; 114572</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98749; 126105</t>
+          <t>75457; 98504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181368; 217953</t>
+          <t>172032; 207922</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>161</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>118129</t>
+          <t>150347</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>156190</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274319</t>
+          <t>266212</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103519; 133311</t>
+          <t>133233; 170716</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135463; 177085</t>
+          <t>101969; 129375</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>250544; 302820</t>
+          <t>241555; 291248</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>448</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>343094</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>286377; 329456</t>
+          <t>318777; 369021</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>348861; 404445</t>
+          <t>278773; 321070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646341; 719224</t>
+          <t>610007; 672454</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>34,89; 57,87</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>43,86; 65,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42,2; 59,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49,47%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>40,74; 53,21</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42,81; 55,69</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43,42; 53,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>50,95%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>44,44; 57,25</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>43,59; 56,9</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46,09; 55,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47,2%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>46,41; 59,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41,54; 52,7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45,35; 54,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>46,79; 54,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>45,94; 52,91</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47,36; 52,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4566292146175043</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.54481164875736</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5035612449581631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>17265</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23436</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40701</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3488674265745656</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.438567642866412</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.421989190556277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13191; 21880</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18866; 28137</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>34108; 47832</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5786713052583446</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6540870514730501</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5917809159509472</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4703095564270977</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4946573526541085</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4820334945163431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>73510</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>71804</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>145314</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4074075709753656</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4280729252321475</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4341895284072873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>63678; 83171</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>62139; 80842</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>130891; 159943</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5321206188861767</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5569193721118302</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5305608213402121</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5095433495801028</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.508615046846197</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5091127993414903</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>101973</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>88044</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>190017</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4443970617057156</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4359005263131847</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4609238724316195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>88935; 114572</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>75457; 98504</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>172032; 207922</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5725018110161567</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5690358186098882</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5570851388121982</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5236658640753147</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4719702915543851</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4998374713732382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>150347</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>115866</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>266212</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4640576326332119</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4153623084281878</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4535405457833814</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>133233; 170716</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101969; 129375</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>241555; 291248</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5946142300330811</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5269972736227001</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5468434027375201</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5035575957947974</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4930161237837379</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4985919607301295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>343094</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>299151</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4678663240910743</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4594324181200523</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4735648160470153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>318777; 369021</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>278773; 321070</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>610007; 672454</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5416091898780893</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5291393604674278</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5220439807616395</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>17265</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>23436</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>40701</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>13191</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>18866</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>34108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>21880</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>28137</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>47832</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>73510</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>71804</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>145314</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>63678</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>62139</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>130891</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>83171</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>80842</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>159943</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>101973</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>88044</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>190017</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>88935</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>75457</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>172032</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>114572</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>98504</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>207922</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>150347</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>115866</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>266212</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>133233</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>101969</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>241555</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>170716</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>129375</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>291248</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>343094</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>299151</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>642245</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>318777</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>278773</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>610007</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>369021</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>321070</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>672454</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>